--- a/Excel/SkillRuneConfig.xlsx
+++ b/Excel/SkillRuneConfig.xlsx
@@ -1834,7 +1834,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L6" s="1">
         <v>0</v>
@@ -1920,7 +1920,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L7" s="1">
         <v>0</v>
@@ -2006,7 +2006,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L8" s="1">
         <v>10</v>
@@ -2092,7 +2092,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L9" s="1">
         <v>10</v>
@@ -2178,7 +2178,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L10" s="1">
         <v>30</v>
@@ -2277,7 +2277,7 @@
         <v>4</v>
       </c>
       <c r="K12" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L12" s="1">
         <v>0</v>
@@ -2363,7 +2363,7 @@
         <v>4</v>
       </c>
       <c r="K13" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L13" s="1">
         <v>0</v>
@@ -2449,7 +2449,7 @@
         <v>4</v>
       </c>
       <c r="K14" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L14" s="1">
         <v>10</v>
@@ -2526,7 +2526,7 @@
         <v>4</v>
       </c>
       <c r="K15" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L15" s="1">
         <v>10</v>
@@ -2612,7 +2612,7 @@
         <v>4</v>
       </c>
       <c r="K16" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L16" s="1">
         <v>20</v>
@@ -2698,7 +2698,7 @@
         <v>4</v>
       </c>
       <c r="K17" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L17" s="1">
         <v>20</v>
@@ -2784,7 +2784,7 @@
         <v>4</v>
       </c>
       <c r="K18" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L18" s="1">
         <v>30</v>
@@ -2874,7 +2874,7 @@
         <v>5</v>
       </c>
       <c r="K20" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L20" s="1">
         <v>0</v>
@@ -2960,7 +2960,7 @@
         <v>5</v>
       </c>
       <c r="K21" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L21" s="1">
         <v>10</v>
@@ -3046,7 +3046,7 @@
         <v>5</v>
       </c>
       <c r="K22" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L22" s="1">
         <v>20</v>
@@ -3132,7 +3132,7 @@
         <v>5</v>
       </c>
       <c r="K23" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L23" s="1">
         <v>30</v>
@@ -3231,7 +3231,7 @@
         <v>1</v>
       </c>
       <c r="K27" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L27" s="1">
         <v>0</v>
@@ -3317,7 +3317,7 @@
         <v>1</v>
       </c>
       <c r="K28" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L28" s="1">
         <v>0</v>
@@ -3403,7 +3403,7 @@
         <v>1</v>
       </c>
       <c r="K29" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L29" s="1">
         <v>10</v>
@@ -3489,7 +3489,7 @@
         <v>1</v>
       </c>
       <c r="K30" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L30" s="1">
         <v>10</v>
@@ -3575,7 +3575,7 @@
         <v>1</v>
       </c>
       <c r="K31" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L31" s="1">
         <v>30</v>
@@ -3674,7 +3674,7 @@
         <v>4</v>
       </c>
       <c r="K33" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L33" s="1">
         <v>0</v>
@@ -3760,7 +3760,7 @@
         <v>4</v>
       </c>
       <c r="K34" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L34" s="1">
         <v>0</v>
@@ -3846,7 +3846,7 @@
         <v>4</v>
       </c>
       <c r="K35" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L35" s="1">
         <v>10</v>
@@ -3932,7 +3932,7 @@
         <v>4</v>
       </c>
       <c r="K36" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L36" s="1">
         <v>10</v>
@@ -4018,7 +4018,7 @@
         <v>4</v>
       </c>
       <c r="K37" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L37" s="1">
         <v>20</v>
@@ -4104,7 +4104,7 @@
         <v>4</v>
       </c>
       <c r="K38" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L38" s="1">
         <v>20</v>
@@ -4190,7 +4190,7 @@
         <v>4</v>
       </c>
       <c r="K39" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L39" s="1">
         <v>30</v>
@@ -4289,7 +4289,7 @@
         <v>5</v>
       </c>
       <c r="K41" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L41" s="1">
         <v>0</v>
@@ -4375,7 +4375,7 @@
         <v>5</v>
       </c>
       <c r="K42" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L42" s="1">
         <v>10</v>
@@ -4461,7 +4461,7 @@
         <v>5</v>
       </c>
       <c r="K43" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L43" s="1">
         <v>20</v>
@@ -4547,7 +4547,7 @@
         <v>5</v>
       </c>
       <c r="K44" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L44" s="1">
         <v>30</v>
@@ -4643,7 +4643,7 @@
         <v>1</v>
       </c>
       <c r="K48" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L48" s="1">
         <v>0</v>
@@ -4729,7 +4729,7 @@
         <v>1</v>
       </c>
       <c r="K49" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L49" s="1">
         <v>0</v>
@@ -4815,7 +4815,7 @@
         <v>1</v>
       </c>
       <c r="K50" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L50" s="1">
         <v>10</v>
@@ -4901,7 +4901,7 @@
         <v>1</v>
       </c>
       <c r="K51" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L51" s="1">
         <v>10</v>
@@ -4987,7 +4987,7 @@
         <v>1</v>
       </c>
       <c r="K52" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L52" s="1">
         <v>30</v>
@@ -5077,7 +5077,7 @@
         <v>4</v>
       </c>
       <c r="K54" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L54" s="1">
         <v>0</v>
@@ -5163,7 +5163,7 @@
         <v>4</v>
       </c>
       <c r="K55" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L55" s="1">
         <v>0</v>
@@ -5249,7 +5249,7 @@
         <v>4</v>
       </c>
       <c r="K56" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L56" s="1">
         <v>10</v>
@@ -5335,7 +5335,7 @@
         <v>4</v>
       </c>
       <c r="K57" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L57" s="1">
         <v>10</v>
@@ -5421,7 +5421,7 @@
         <v>4</v>
       </c>
       <c r="K58" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L58" s="1">
         <v>20</v>
@@ -5507,7 +5507,7 @@
         <v>4</v>
       </c>
       <c r="K59" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L59" s="1">
         <v>20</v>
@@ -5593,7 +5593,7 @@
         <v>4</v>
       </c>
       <c r="K60" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L60" s="1">
         <v>30</v>
@@ -5683,7 +5683,7 @@
         <v>5</v>
       </c>
       <c r="K62" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L62" s="1">
         <v>0</v>
@@ -5769,7 +5769,7 @@
         <v>5</v>
       </c>
       <c r="K63" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L63" s="1">
         <v>10</v>
@@ -5855,7 +5855,7 @@
         <v>5</v>
       </c>
       <c r="K64" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L64" s="1">
         <v>30</v>
